--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,9 +470,65 @@
         <v>#ee5d5d</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>صوصات</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Sauces</v>
+      </c>
+      <c r="D6" t="str">
+        <v>#ee5d9d</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>دجاج</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="D7" t="str">
+        <v>#ee5d6d</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>خضار</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Vegetables</v>
+      </c>
+      <c r="D8" t="str">
+        <v>#ee5d7d</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>فواكه</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Fruits</v>
+      </c>
+      <c r="D9" t="str">
+        <v>#ee5d87d</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -622,9 +622,26 @@
         <v>soap</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>1755827699112</v>
+      </c>
+      <c r="B6" t="str">
+        <v>لحوم1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>لحوم</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="str">
+        <v>box</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -639,9 +639,672 @@
         <v>box</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>مأكولات1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>مأكولات2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="str">
+        <v>مشروبات1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>مشروبات</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>مشروبات2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>مشروبات</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>مأكولات3</v>
+      </c>
+      <c r="C11" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="str">
+        <v>مأكولات4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" t="str">
+        <v>مأكولات6</v>
+      </c>
+      <c r="C13" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="C14" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="str">
+        <v>مأكولات60</v>
+      </c>
+      <c r="C15" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="str">
+        <v>مأكولات10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>مأكولات50</v>
+      </c>
+      <c r="C17" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="str">
+        <v>مأكولات30</v>
+      </c>
+      <c r="C18" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="str">
+        <v>منظفات1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>منظفات</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="str">
+        <v>مأكولات101</v>
+      </c>
+      <c r="C20" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>مأكولات102</v>
+      </c>
+      <c r="C21" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>مأكولات103</v>
+      </c>
+      <c r="C22" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>مأكولات104</v>
+      </c>
+      <c r="C23" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>مأكولات105</v>
+      </c>
+      <c r="C24" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>مأكولات106</v>
+      </c>
+      <c r="C25" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>مأكولات107</v>
+      </c>
+      <c r="C26" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>مأكولات108</v>
+      </c>
+      <c r="C27" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>مأكولات109</v>
+      </c>
+      <c r="C28" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>مأكولات110</v>
+      </c>
+      <c r="C29" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>مأكولات111</v>
+      </c>
+      <c r="C30" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>مأكولات112</v>
+      </c>
+      <c r="C31" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="str">
+        <v>مأكولات113</v>
+      </c>
+      <c r="C32" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>مأكولات114</v>
+      </c>
+      <c r="C33" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="str">
+        <v>مأكولات115</v>
+      </c>
+      <c r="C34" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="str">
+        <v>مأكولات116</v>
+      </c>
+      <c r="C35" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="str">
+        <v>مأكولات117</v>
+      </c>
+      <c r="C36" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="str">
+        <v>مأكولات118</v>
+      </c>
+      <c r="C37" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="str">
+        <v>مأكولات119</v>
+      </c>
+      <c r="C38" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="str">
+        <v>مأكولات120</v>
+      </c>
+      <c r="C39" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="str">
+        <v>مأكولات121</v>
+      </c>
+      <c r="C40" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="str">
+        <v>مأكولات122</v>
+      </c>
+      <c r="C41" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="str">
+        <v>مأكولات123</v>
+      </c>
+      <c r="C42" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="str">
+        <v>مأكولات124</v>
+      </c>
+      <c r="C43" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="str">
+        <v>مأكولات125</v>
+      </c>
+      <c r="C44" t="str">
+        <v>مأكولات</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>box</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="str">
+        <v>صوصات1</v>
+      </c>
+      <c r="C45" t="str">
+        <v>صوصات</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="str">
+        <v>box</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -425,7 +425,7 @@
         <v>utensils</v>
       </c>
       <c r="D2" t="str">
-        <v>#3498db</v>
+        <v>#9ccdf2</v>
       </c>
     </row>
     <row r="3">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -453,7 +453,7 @@
         <v>spray-can</v>
       </c>
       <c r="D4" t="str">
-        <v>#2ecc71</v>
+        <v>#6ddf9c</v>
       </c>
     </row>
     <row r="5">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -439,7 +439,7 @@
         <v>glass-cheers</v>
       </c>
       <c r="D3" t="str">
-        <v>#e74c3c</v>
+        <v>#e8887d</v>
       </c>
     </row>
     <row r="4">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -467,7 +467,7 @@
         <v>folder</v>
       </c>
       <c r="D5" t="str">
-        <v>#ee5d5d</v>
+        <v>#e0e59a</v>
       </c>
     </row>
     <row r="6">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -481,7 +481,7 @@
         <v>Sauces</v>
       </c>
       <c r="D6" t="str">
-        <v>#ee5d9d</v>
+        <v>#f27db0</v>
       </c>
     </row>
     <row r="7">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -495,7 +495,7 @@
         <v>Chicken</v>
       </c>
       <c r="D7" t="str">
-        <v>#ee5d6d</v>
+        <v>#7ceed2</v>
       </c>
     </row>
     <row r="8">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -509,7 +509,7 @@
         <v>Vegetables</v>
       </c>
       <c r="D8" t="str">
-        <v>#ee5d7d</v>
+        <v>#777bee</v>
       </c>
     </row>
     <row r="9">

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -523,7 +523,7 @@
         <v>Fruits</v>
       </c>
       <c r="D9" t="str">
-        <v>#ee5d87d</v>
+        <v>#d17ee2</v>
       </c>
     </row>
   </sheetData>
